--- a/panchang-data/Patna2026.xlsx
+++ b/panchang-data/Patna2026.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9518" uniqueCount="5403">
   <si>
     <t>दिनाङ्क</t>
   </si>
@@ -16234,6 +16234,9 @@
   </si>
   <si>
     <t>121°05'08.24</t>
+  </si>
+  <si>
+    <t>ज्येष्ठ अधिक</t>
   </si>
 </sst>
 </file>
@@ -16723,7 +16726,7 @@
         <v>46023</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>29</v>
@@ -16809,7 +16812,7 @@
         <v>46024</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>50</v>
@@ -16895,7 +16898,7 @@
         <v>46025</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>70</v>
@@ -16981,7 +16984,7 @@
         <v>46026</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>89</v>
@@ -17067,7 +17070,7 @@
         <v>46027</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>108</v>
@@ -17153,7 +17156,7 @@
         <v>46028</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>125</v>
@@ -17239,7 +17242,7 @@
         <v>46029</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>143</v>
@@ -17325,7 +17328,7 @@
         <v>46030</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>29</v>
@@ -17411,7 +17414,7 @@
         <v>46031</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>50</v>
@@ -17497,7 +17500,7 @@
         <v>46032</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>70</v>
@@ -17583,7 +17586,7 @@
         <v>46033</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>89</v>
@@ -17669,7 +17672,7 @@
         <v>46034</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>108</v>
@@ -17755,7 +17758,7 @@
         <v>46035</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>125</v>
@@ -17841,7 +17844,7 @@
         <v>46036</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>143</v>
@@ -17927,7 +17930,7 @@
         <v>46037</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>29</v>
@@ -18013,7 +18016,7 @@
         <v>46038</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>50</v>
@@ -18099,7 +18102,7 @@
         <v>46039</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>70</v>
@@ -18185,7 +18188,7 @@
         <v>46040</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>89</v>
@@ -18271,7 +18274,7 @@
         <v>46041</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>108</v>
@@ -18357,7 +18360,7 @@
         <v>46042</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>125</v>
@@ -18443,7 +18446,7 @@
         <v>46043</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>143</v>
@@ -18529,7 +18532,7 @@
         <v>46044</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>29</v>
@@ -18615,7 +18618,7 @@
         <v>46045</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>50</v>
@@ -18701,7 +18704,7 @@
         <v>46046</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>70</v>
@@ -18787,7 +18790,7 @@
         <v>46047</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>89</v>
@@ -18873,7 +18876,7 @@
         <v>46048</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>108</v>
@@ -18959,7 +18962,7 @@
         <v>46049</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>125</v>
@@ -19045,7 +19048,7 @@
         <v>46050</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>143</v>
@@ -19131,7 +19134,7 @@
         <v>46051</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>29</v>
@@ -19217,7 +19220,7 @@
         <v>46052</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>50</v>
@@ -19303,7 +19306,7 @@
         <v>46053</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>70</v>
@@ -19389,7 +19392,7 @@
         <v>46054</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>88</v>
+        <v>567</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>89</v>
@@ -19475,7 +19478,7 @@
         <v>46055</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>108</v>
@@ -19561,7 +19564,7 @@
         <v>46056</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>125</v>
@@ -19647,7 +19650,7 @@
         <v>46057</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>143</v>
@@ -19733,7 +19736,7 @@
         <v>46058</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>29</v>
@@ -19819,7 +19822,7 @@
         <v>46059</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>50</v>
@@ -19905,7 +19908,7 @@
         <v>46060</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>70</v>
@@ -19991,7 +19994,7 @@
         <v>46061</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>89</v>
@@ -20077,7 +20080,7 @@
         <v>46062</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -20163,7 +20166,7 @@
         <v>46063</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>125</v>
@@ -20249,7 +20252,7 @@
         <v>46064</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>143</v>
@@ -20335,7 +20338,7 @@
         <v>46065</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>29</v>
@@ -20421,7 +20424,7 @@
         <v>46066</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>50</v>
@@ -20507,7 +20510,7 @@
         <v>46067</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>70</v>
@@ -20593,7 +20596,7 @@
         <v>46068</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>89</v>
@@ -20679,7 +20682,7 @@
         <v>46069</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>108</v>
@@ -20765,7 +20768,7 @@
         <v>46070</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>125</v>
@@ -20851,7 +20854,7 @@
         <v>46071</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>143</v>
@@ -20937,7 +20940,7 @@
         <v>46072</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>29</v>
@@ -21023,7 +21026,7 @@
         <v>46073</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>50</v>
@@ -21109,7 +21112,7 @@
         <v>46074</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>70</v>
@@ -21195,7 +21198,7 @@
         <v>46075</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>89</v>
@@ -21281,7 +21284,7 @@
         <v>46076</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>108</v>
@@ -21367,7 +21370,7 @@
         <v>46077</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>125</v>
@@ -21453,7 +21456,7 @@
         <v>46078</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>143</v>
@@ -21539,7 +21542,7 @@
         <v>46079</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>29</v>
@@ -21625,7 +21628,7 @@
         <v>46080</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>50</v>
@@ -21711,7 +21714,7 @@
         <v>46081</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>70</v>
@@ -21797,7 +21800,7 @@
         <v>46082</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>89</v>
@@ -21883,7 +21886,7 @@
         <v>46083</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>108</v>
@@ -21969,7 +21972,7 @@
         <v>46084</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>567</v>
+        <v>1006</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>125</v>
@@ -22055,7 +22058,7 @@
         <v>46085</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>143</v>
@@ -22141,7 +22144,7 @@
         <v>46086</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>29</v>
@@ -22227,7 +22230,7 @@
         <v>46087</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>50</v>
@@ -22313,7 +22316,7 @@
         <v>46088</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>70</v>
@@ -22399,7 +22402,7 @@
         <v>46089</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>89</v>
@@ -22485,7 +22488,7 @@
         <v>46090</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>108</v>
@@ -22571,7 +22574,7 @@
         <v>46091</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>125</v>
@@ -22657,7 +22660,7 @@
         <v>46092</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>143</v>
@@ -22743,7 +22746,7 @@
         <v>46093</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>29</v>
@@ -22829,7 +22832,7 @@
         <v>46094</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>50</v>
@@ -22915,7 +22918,7 @@
         <v>46095</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>70</v>
@@ -23001,7 +23004,7 @@
         <v>46096</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>89</v>
@@ -23087,7 +23090,7 @@
         <v>46097</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>108</v>
@@ -23173,7 +23176,7 @@
         <v>46098</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>125</v>
@@ -23259,7 +23262,7 @@
         <v>46099</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>143</v>
@@ -23345,7 +23348,7 @@
         <v>46100</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>29</v>
@@ -23431,7 +23434,7 @@
         <v>46101</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>50</v>
@@ -23517,7 +23520,7 @@
         <v>46102</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>70</v>
@@ -23603,7 +23606,7 @@
         <v>46103</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>89</v>
@@ -23689,7 +23692,7 @@
         <v>46104</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>108</v>
@@ -23775,7 +23778,7 @@
         <v>46105</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>125</v>
@@ -23861,7 +23864,7 @@
         <v>46106</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>143</v>
@@ -23947,7 +23950,7 @@
         <v>46107</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>29</v>
@@ -24033,7 +24036,7 @@
         <v>46108</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>50</v>
@@ -24119,7 +24122,7 @@
         <v>46109</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>70</v>
@@ -24205,7 +24208,7 @@
         <v>46110</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>89</v>
@@ -24291,7 +24294,7 @@
         <v>46111</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>108</v>
@@ -24377,7 +24380,7 @@
         <v>46112</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>125</v>
@@ -24463,7 +24466,7 @@
         <v>46113</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>143</v>
@@ -24549,7 +24552,7 @@
         <v>46114</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>1006</v>
+        <v>1447</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>29</v>
@@ -24635,7 +24638,7 @@
         <v>46115</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>50</v>
@@ -24721,7 +24724,7 @@
         <v>46116</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>70</v>
@@ -24807,7 +24810,7 @@
         <v>46117</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>89</v>
@@ -24893,7 +24896,7 @@
         <v>46118</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>108</v>
@@ -24979,7 +24982,7 @@
         <v>46119</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>125</v>
@@ -25065,7 +25068,7 @@
         <v>46120</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>143</v>
@@ -25151,7 +25154,7 @@
         <v>46121</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>29</v>
@@ -25237,7 +25240,7 @@
         <v>46122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>50</v>
@@ -25323,7 +25326,7 @@
         <v>46123</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>70</v>
@@ -25409,7 +25412,7 @@
         <v>46124</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>89</v>
@@ -25495,7 +25498,7 @@
         <v>46125</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>108</v>
@@ -25581,7 +25584,7 @@
         <v>46126</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>125</v>
@@ -25667,7 +25670,7 @@
         <v>46127</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>143</v>
@@ -25753,7 +25756,7 @@
         <v>46128</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>29</v>
@@ -25839,7 +25842,7 @@
         <v>46129</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>50</v>
@@ -25925,7 +25928,7 @@
         <v>46130</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>70</v>
@@ -26011,7 +26014,7 @@
         <v>46131</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>89</v>
@@ -26097,7 +26100,7 @@
         <v>46132</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>108</v>
@@ -26183,7 +26186,7 @@
         <v>46133</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>125</v>
@@ -26269,7 +26272,7 @@
         <v>46134</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>143</v>
@@ -26355,7 +26358,7 @@
         <v>46135</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>29</v>
@@ -26441,7 +26444,7 @@
         <v>46136</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>50</v>
@@ -26527,7 +26530,7 @@
         <v>46137</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>70</v>
@@ -26613,7 +26616,7 @@
         <v>46138</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>89</v>
@@ -26699,7 +26702,7 @@
         <v>46139</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>108</v>
@@ -26785,7 +26788,7 @@
         <v>46140</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>125</v>
@@ -26871,7 +26874,7 @@
         <v>46141</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>143</v>
@@ -26957,7 +26960,7 @@
         <v>46142</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>29</v>
@@ -27043,7 +27046,7 @@
         <v>46143</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1447</v>
+        <v>1871</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>50</v>
@@ -27129,7 +27132,7 @@
         <v>46144</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1871</v>
+        <v>2307</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>70</v>
@@ -27215,7 +27218,7 @@
         <v>46145</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1871</v>
+        <v>2307</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>89</v>
@@ -27301,7 +27304,7 @@
         <v>46146</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>1871</v>
+        <v>2307</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>108</v>
@@ -27387,7 +27390,7 @@
         <v>46147</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>1871</v>
+        <v>2307</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>125</v>
@@ -27473,7 +27476,7 @@
         <v>46148</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>1871</v>
+        <v>2307</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>143</v>
@@ -27559,7 +27562,7 @@
         <v>46149</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>1871</v>
+        <v>2307</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>29</v>
@@ -27645,7 +27648,7 @@
         <v>46150</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>1871</v>
+        <v>2307</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>50</v>
@@ -27731,7 +27734,7 @@
         <v>46151</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1871</v>
+        <v>2307</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>70</v>
@@ -27817,7 +27820,7 @@
         <v>46152</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1871</v>
+        <v>2307</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>89</v>
@@ -27903,7 +27906,7 @@
         <v>46153</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1871</v>
+        <v>2307</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>108</v>
@@ -27989,7 +27992,7 @@
         <v>46154</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>1871</v>
+        <v>2307</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>125</v>
@@ -28075,7 +28078,7 @@
         <v>46155</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1871</v>
+        <v>2307</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>143</v>
@@ -28161,7 +28164,7 @@
         <v>46156</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1871</v>
+        <v>2307</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>29</v>
@@ -28247,7 +28250,7 @@
         <v>46157</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>1871</v>
+        <v>2307</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>50</v>
@@ -28333,7 +28336,7 @@
         <v>46158</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>1871</v>
+        <v>2307</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>70</v>
@@ -28419,7 +28422,7 @@
         <v>46159</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>1871</v>
+        <v>5402</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>89</v>
@@ -28505,7 +28508,7 @@
         <v>46160</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>1871</v>
+        <v>5402</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>108</v>
@@ -28591,7 +28594,7 @@
         <v>46161</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>1871</v>
+        <v>5402</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>125</v>
@@ -28677,7 +28680,7 @@
         <v>46162</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>1871</v>
+        <v>5402</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>143</v>
@@ -28763,7 +28766,7 @@
         <v>46163</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>1871</v>
+        <v>5402</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>29</v>
@@ -28849,7 +28852,7 @@
         <v>46164</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>1871</v>
+        <v>5402</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>50</v>
@@ -28935,7 +28938,7 @@
         <v>46165</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>1871</v>
+        <v>5402</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>70</v>
@@ -29021,7 +29024,7 @@
         <v>46166</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>1871</v>
+        <v>5402</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>89</v>
@@ -29107,7 +29110,7 @@
         <v>46167</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>1871</v>
+        <v>5402</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>108</v>
@@ -29193,7 +29196,7 @@
         <v>46168</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>1871</v>
+        <v>5402</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>125</v>
@@ -29279,7 +29282,7 @@
         <v>46169</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>1871</v>
+        <v>5402</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>143</v>
@@ -29365,7 +29368,7 @@
         <v>46170</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>1871</v>
+        <v>5402</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>29</v>
@@ -29451,7 +29454,7 @@
         <v>46171</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>1871</v>
+        <v>5402</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>50</v>
@@ -29537,7 +29540,7 @@
         <v>46172</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>1871</v>
+        <v>5402</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>70</v>
@@ -29623,7 +29626,7 @@
         <v>46173</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>1871</v>
+        <v>5402</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>89</v>
@@ -29709,7 +29712,7 @@
         <v>46174</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>2307</v>
+        <v>5402</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>108</v>
@@ -29795,7 +29798,7 @@
         <v>46175</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>2307</v>
+        <v>5402</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>125</v>
@@ -29881,7 +29884,7 @@
         <v>46176</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>2307</v>
+        <v>5402</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>143</v>
@@ -29967,7 +29970,7 @@
         <v>46177</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>2307</v>
+        <v>5402</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>29</v>
@@ -30053,7 +30056,7 @@
         <v>46178</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>2307</v>
+        <v>5402</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>50</v>
@@ -30139,7 +30142,7 @@
         <v>46179</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>2307</v>
+        <v>5402</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>70</v>
@@ -30225,7 +30228,7 @@
         <v>46180</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>2307</v>
+        <v>5402</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>89</v>
@@ -30311,7 +30314,7 @@
         <v>46181</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>2307</v>
+        <v>5402</v>
       </c>
       <c r="C160" s="2" t="s">
         <v>108</v>
@@ -30397,7 +30400,7 @@
         <v>46182</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>2307</v>
+        <v>5402</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>125</v>
@@ -30483,7 +30486,7 @@
         <v>46183</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>2307</v>
+        <v>5402</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>143</v>
@@ -30569,7 +30572,7 @@
         <v>46184</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>2307</v>
+        <v>5402</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>29</v>
@@ -30655,7 +30658,7 @@
         <v>46185</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>2307</v>
+        <v>5402</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>50</v>
@@ -30741,7 +30744,7 @@
         <v>46186</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>2307</v>
+        <v>5402</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>70</v>
@@ -30827,7 +30830,7 @@
         <v>46187</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>2307</v>
+        <v>5402</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>89</v>
@@ -30913,7 +30916,7 @@
         <v>46188</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>2307</v>
+        <v>5402</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>108</v>
